--- a/Java hint.xlsx
+++ b/Java hint.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="132" windowWidth="20112" windowHeight="7932" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="240" yWindow="132" windowWidth="20112" windowHeight="7932" firstSheet="1" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Иструменты" sheetId="1" r:id="rId1"/>
@@ -16,13 +16,14 @@
     <sheet name="Exceptions" sheetId="8" r:id="rId7"/>
     <sheet name="Concurrency" sheetId="9" r:id="rId8"/>
     <sheet name="Regex" sheetId="10" r:id="rId9"/>
+    <sheet name="API" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="144525" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="275">
   <si>
     <t>Структура пакетов</t>
   </si>
@@ -8065,6 +8066,30 @@
       </rPr>
       <t>). Это полиморфизм в действии - вызов виртуального метода. НО, instanceMethod должен присутствовать в ClassName.</t>
     </r>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>Более низкоуровневый эквивалент (незначительно меньше кода)</t>
+  </si>
+  <si>
+    <t>Objects.equals(obj1, obj2)</t>
+  </si>
+  <si>
+    <t>obj1.equals(obj2)</t>
+  </si>
+  <si>
+    <t>P.S. equals() должен быть переопределён для всех объектов, участвующих в сравнении</t>
+  </si>
+  <si>
+    <t>Objects.deepEquals(obj1, obj2)</t>
+  </si>
+  <si>
+    <t>Arrays.equals(arr1, arr2) (одномерный массив)</t>
+  </si>
+  <si>
+    <t>Arrays.deepEquals(arr1, arr2) (многомерный массив объектов; можно и одномерный, но лучше предыдущий вариант, особенно для примитивных типов)</t>
   </si>
 </sst>
 </file>
@@ -8242,7 +8267,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -8342,11 +8367,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -8469,6 +8531,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8505,35 +8597,32 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8973,6 +9062,67 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.21875" customWidth="1"/>
+    <col min="2" max="2" width="4.109375" style="78" customWidth="1"/>
+    <col min="3" max="3" width="132.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="15"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="15" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="84" t="s">
+        <v>269</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="85" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="82" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="86"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="81" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H13"/>
@@ -9189,12 +9339,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
@@ -9255,20 +9405,20 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
     </row>
     <row r="8" spans="1:7" s="31" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C9" s="35"/>
@@ -9280,26 +9430,26 @@
       <c r="B10" s="52"/>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="55"/>
+      <c r="B11" s="65"/>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="55"/>
+      <c r="B12" s="65"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63" t="s">
+      <c r="B14" s="73"/>
+      <c r="C14" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="63"/>
+      <c r="D14" s="73"/>
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
@@ -9383,21 +9533,21 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="59"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="69"/>
       <c r="E20" s="29"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="62"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="72"/>
     </row>
     <row r="22" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="30"/>
@@ -9406,12 +9556,12 @@
       <c r="D22" s="30"/>
     </row>
     <row r="23" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
@@ -9420,20 +9570,20 @@
       <c r="D24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="68"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="59"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="66" t="s">
+      <c r="A26" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="68"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="59"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="21"/>
@@ -9442,28 +9592,28 @@
       <c r="D27" s="23"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="68"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="59"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="66" t="s">
+      <c r="A29" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="B29" s="67"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="68"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="59"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="66" t="s">
+      <c r="A30" s="57" t="s">
         <v>265</v>
       </c>
-      <c r="B30" s="67"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="68"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="59"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="32"/>
@@ -9472,44 +9622,44 @@
       <c r="D31" s="34"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="67"/>
-      <c r="C32" s="67"/>
-      <c r="D32" s="68"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="59"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="73" t="s">
+      <c r="A34" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="74"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="75"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="63"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="67"/>
-      <c r="C35" s="67"/>
-      <c r="D35" s="68"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="59"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="66" t="s">
+      <c r="A36" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="68"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="59"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="36"/>
@@ -9518,20 +9668,20 @@
       <c r="D37" s="38"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="67"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="68"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="59"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="71"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="56"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="24"/>
@@ -9547,16 +9697,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
@@ -9570,6 +9710,16 @@
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
